--- a/评测/法规评测集.xlsx
+++ b/评测/法规评测集.xlsx
@@ -5821,12 +5821,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">第六十六条｜第八十三条</t>
+          <t xml:space="preserve">第六十六条｜第八十四条</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">第六十六条 期货公司有下列行为之一的，责令改正，给予警告，没收违法所得，｜第八十三条 证券公司违反本条例的规定，有下列情形之一的，责令改正，给予警</t>
+          <t xml:space="preserve">第六十六条 期货公司有下列行为之一的，责令改正，给予警告，没收违法所得，｜第八十四条 证券公司违反本条例的规定，有下列情形之一的，责令改正，给予警</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -5858,7 +5858,11 @@
 (五)从事证券资产管理业务，接受一个客户的单笔委托资产价值低于规定的最低限额。</t>
         </is>
       </c>
-      <c r="K103"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">锚点修正：原先写的是《证券公司监督管理条例》第八十三条，但该条讲的是客户招揽、投资建议、代客买卖，与适当性无关；第八十四条才是适当性违规罚则（了解客户身份财产经验风险偏好、推荐与客户情况相适应、讲解业务规则并揭示风险、签订合同）。</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
